--- a/targeted/peak_bounds.xlsx
+++ b/targeted/peak_bounds.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willi\Documents\PARAGON\targeted\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Will\PARAGON\targeted\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D876CD-D515-49EF-AC34-DCC5F9395100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{F5906ABD-DA83-41F4-BE07-820E56D6A73A}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="peak_bounds" sheetId="1" r:id="rId1"/>
@@ -952,7 +951,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1792,18 +1791,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2E6E52-81B1-4EB2-A3E3-96AA3152087B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K1085"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" customWidth="1"/>
-    <col min="4" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1838,7 +1837,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>248</v>
       </c>
@@ -1899,7 +1898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>247</v>
       </c>
@@ -1928,7 +1927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>246</v>
       </c>
@@ -1957,7 +1956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1989,7 +1988,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>248</v>
       </c>
@@ -2018,7 +2017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>247</v>
       </c>
@@ -2047,7 +2046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>246</v>
       </c>
@@ -2076,7 +2075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2111,7 +2110,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>248</v>
       </c>
@@ -2140,7 +2139,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>247</v>
       </c>
@@ -2169,7 +2168,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>246</v>
       </c>
@@ -2201,7 +2200,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -2233,7 +2232,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>248</v>
       </c>
@@ -2262,7 +2261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>247</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>246</v>
       </c>
@@ -2320,7 +2319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2352,7 +2351,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>248</v>
       </c>
@@ -2381,7 +2380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>247</v>
       </c>
@@ -2410,7 +2409,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>246</v>
       </c>
@@ -2439,7 +2438,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>248</v>
       </c>
@@ -2500,7 +2499,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>247</v>
       </c>
@@ -2529,7 +2528,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>246</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2590,7 +2589,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>248</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>247</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>246</v>
       </c>
@@ -2686,7 +2685,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -2718,7 +2717,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>248</v>
       </c>
@@ -2750,7 +2749,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>247</v>
       </c>
@@ -2782,7 +2781,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>246</v>
       </c>
@@ -2814,7 +2813,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>248</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>247</v>
       </c>
@@ -2901,7 +2900,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>246</v>
       </c>
@@ -2930,7 +2929,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -2962,7 +2961,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>248</v>
       </c>
@@ -2991,7 +2990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>247</v>
       </c>
@@ -3020,7 +3019,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>246</v>
       </c>
@@ -3049,7 +3048,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -3081,7 +3080,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>248</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>247</v>
       </c>
@@ -3139,7 +3138,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>246</v>
       </c>
@@ -3168,7 +3167,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -3200,7 +3199,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>248</v>
       </c>
@@ -3229,7 +3228,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>247</v>
       </c>
@@ -3258,7 +3257,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>246</v>
       </c>
@@ -3287,7 +3286,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -3316,7 +3315,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>248</v>
       </c>
@@ -3345,7 +3344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>247</v>
       </c>
@@ -3374,7 +3373,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>246</v>
       </c>
@@ -3403,7 +3402,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -3435,7 +3434,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>248</v>
       </c>
@@ -3467,7 +3466,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>247</v>
       </c>
@@ -3499,7 +3498,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>246</v>
       </c>
@@ -3531,7 +3530,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -3560,7 +3559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>248</v>
       </c>
@@ -3589,7 +3588,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>247</v>
       </c>
@@ -3618,7 +3617,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>246</v>
       </c>
@@ -3647,7 +3646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -3679,7 +3678,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>248</v>
       </c>
@@ -3708,7 +3707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>247</v>
       </c>
@@ -3737,7 +3736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>246</v>
       </c>
@@ -3766,7 +3765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -3798,7 +3797,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>248</v>
       </c>
@@ -3827,7 +3826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>247</v>
       </c>
@@ -3856,7 +3855,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>246</v>
       </c>
@@ -3885,7 +3884,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -3920,7 +3919,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>248</v>
       </c>
@@ -3949,7 +3948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>247</v>
       </c>
@@ -3978,7 +3977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>246</v>
       </c>
@@ -4007,7 +4006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>10</v>
       </c>
@@ -4039,7 +4038,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>248</v>
       </c>
@@ -4068,7 +4067,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>247</v>
       </c>
@@ -4097,7 +4096,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>246</v>
       </c>
@@ -4126,7 +4125,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -4155,7 +4154,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>248</v>
       </c>
@@ -4184,7 +4183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>247</v>
       </c>
@@ -4213,7 +4212,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>246</v>
       </c>
@@ -4242,7 +4241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>248</v>
       </c>
@@ -4303,7 +4302,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>247</v>
       </c>
@@ -4332,7 +4331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>246</v>
       </c>
@@ -4361,7 +4360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -4390,7 +4389,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>248</v>
       </c>
@@ -4419,7 +4418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>247</v>
       </c>
@@ -4448,7 +4447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>246</v>
       </c>
@@ -4477,7 +4476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -4506,7 +4505,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -4535,7 +4534,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>247</v>
       </c>
@@ -4564,7 +4563,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>246</v>
       </c>
@@ -4596,7 +4595,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>10</v>
       </c>
@@ -4625,7 +4624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>248</v>
       </c>
@@ -4654,7 +4653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>247</v>
       </c>
@@ -4683,7 +4682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>246</v>
       </c>
@@ -4712,7 +4711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>10</v>
       </c>
@@ -4747,7 +4746,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>248</v>
       </c>
@@ -4776,7 +4775,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>247</v>
       </c>
@@ -4805,7 +4804,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>246</v>
       </c>
@@ -4834,7 +4833,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -4866,7 +4865,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>248</v>
       </c>
@@ -4895,7 +4894,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>247</v>
       </c>
@@ -4924,7 +4923,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>246</v>
       </c>
@@ -4953,7 +4952,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>248</v>
       </c>
@@ -5014,7 +5013,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>247</v>
       </c>
@@ -5043,7 +5042,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>246</v>
       </c>
@@ -5072,7 +5071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>10</v>
       </c>
@@ -5101,7 +5100,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>248</v>
       </c>
@@ -5130,7 +5129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>247</v>
       </c>
@@ -5159,7 +5158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>246</v>
       </c>
@@ -5191,7 +5190,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -5220,7 +5219,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>248</v>
       </c>
@@ -5249,7 +5248,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>247</v>
       </c>
@@ -5278,7 +5277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>246</v>
       </c>
@@ -5307,7 +5306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>10</v>
       </c>
@@ -5336,7 +5335,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>248</v>
       </c>
@@ -5365,7 +5364,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>247</v>
       </c>
@@ -5394,7 +5393,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>246</v>
       </c>
@@ -5423,7 +5422,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>10</v>
       </c>
@@ -5452,7 +5451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>248</v>
       </c>
@@ -5481,7 +5480,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>247</v>
       </c>
@@ -5510,7 +5509,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>246</v>
       </c>
@@ -5539,7 +5538,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>10</v>
       </c>
@@ -5568,7 +5567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>248</v>
       </c>
@@ -5597,7 +5596,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -5626,7 +5625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>246</v>
       </c>
@@ -5655,7 +5654,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -5684,7 +5683,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>248</v>
       </c>
@@ -5716,7 +5715,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>247</v>
       </c>
@@ -5745,7 +5744,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>246</v>
       </c>
@@ -5774,7 +5773,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -5806,7 +5805,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>248</v>
       </c>
@@ -5835,7 +5834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>247</v>
       </c>
@@ -5864,7 +5863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>246</v>
       </c>
@@ -5893,7 +5892,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>10</v>
       </c>
@@ -5925,7 +5924,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>248</v>
       </c>
@@ -5954,7 +5953,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>247</v>
       </c>
@@ -5983,7 +5982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>246</v>
       </c>
@@ -6015,7 +6014,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -6044,7 +6043,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>248</v>
       </c>
@@ -6073,7 +6072,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>247</v>
       </c>
@@ -6102,7 +6101,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>246</v>
       </c>
@@ -6131,7 +6130,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -6160,7 +6159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>248</v>
       </c>
@@ -6189,7 +6188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>247</v>
       </c>
@@ -6218,7 +6217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>246</v>
       </c>
@@ -6247,7 +6246,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -6276,7 +6275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>248</v>
       </c>
@@ -6305,7 +6304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>247</v>
       </c>
@@ -6334,7 +6333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>246</v>
       </c>
@@ -6363,7 +6362,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>10</v>
       </c>
@@ -6392,7 +6391,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>248</v>
       </c>
@@ -6421,7 +6420,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>247</v>
       </c>
@@ -6450,7 +6449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>246</v>
       </c>
@@ -6479,7 +6478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -6508,7 +6507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>248</v>
       </c>
@@ -6537,7 +6536,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>247</v>
       </c>
@@ -6566,7 +6565,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>246</v>
       </c>
@@ -6595,7 +6594,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>10</v>
       </c>
@@ -6627,7 +6626,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>248</v>
       </c>
@@ -6659,7 +6658,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>247</v>
       </c>
@@ -6691,7 +6690,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>246</v>
       </c>
@@ -6723,7 +6722,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>10</v>
       </c>
@@ -6755,7 +6754,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>248</v>
       </c>
@@ -6784,7 +6783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>247</v>
       </c>
@@ -6813,7 +6812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>246</v>
       </c>
@@ -6842,7 +6841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -6874,7 +6873,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>248</v>
       </c>
@@ -6903,7 +6902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>247</v>
       </c>
@@ -6932,7 +6931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>246</v>
       </c>
@@ -6961,7 +6960,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>10</v>
       </c>
@@ -6990,7 +6989,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>248</v>
       </c>
@@ -7022,7 +7021,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>247</v>
       </c>
@@ -7051,7 +7050,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>246</v>
       </c>
@@ -7083,7 +7082,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>10</v>
       </c>
@@ -7112,7 +7111,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>248</v>
       </c>
@@ -7141,7 +7140,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>247</v>
       </c>
@@ -7170,7 +7169,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>246</v>
       </c>
@@ -7199,7 +7198,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>10</v>
       </c>
@@ -7228,7 +7227,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>248</v>
       </c>
@@ -7257,7 +7256,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>247</v>
       </c>
@@ -7286,7 +7285,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>246</v>
       </c>
@@ -7315,7 +7314,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>10</v>
       </c>
@@ -7344,7 +7343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>248</v>
       </c>
@@ -7376,7 +7375,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>247</v>
       </c>
@@ -7405,7 +7404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>246</v>
       </c>
@@ -7434,7 +7433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>10</v>
       </c>
@@ -7466,7 +7465,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>248</v>
       </c>
@@ -7498,7 +7497,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>247</v>
       </c>
@@ -7530,7 +7529,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>246</v>
       </c>
@@ -7562,7 +7561,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -7591,7 +7590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>248</v>
       </c>
@@ -7623,7 +7622,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>247</v>
       </c>
@@ -7652,7 +7651,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>246</v>
       </c>
@@ -7681,7 +7680,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -7710,7 +7709,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>248</v>
       </c>
@@ -7739,7 +7738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>247</v>
       </c>
@@ -7768,7 +7767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>246</v>
       </c>
@@ -7797,7 +7796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>10</v>
       </c>
@@ -7829,7 +7828,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>248</v>
       </c>
@@ -7861,7 +7860,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>247</v>
       </c>
@@ -7893,7 +7892,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>246</v>
       </c>
@@ -7925,7 +7924,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -7954,7 +7953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>248</v>
       </c>
@@ -7983,7 +7982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>247</v>
       </c>
@@ -8012,7 +8011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>246</v>
       </c>
@@ -8041,7 +8040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -8070,7 +8069,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>248</v>
       </c>
@@ -8099,7 +8098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>247</v>
       </c>
@@ -8128,7 +8127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>246</v>
       </c>
@@ -8157,7 +8156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>10</v>
       </c>
@@ -8186,7 +8185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>248</v>
       </c>
@@ -8215,7 +8214,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>247</v>
       </c>
@@ -8244,7 +8243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>246</v>
       </c>
@@ -8273,7 +8272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>10</v>
       </c>
@@ -8302,7 +8301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>248</v>
       </c>
@@ -8331,7 +8330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>247</v>
       </c>
@@ -8360,7 +8359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>246</v>
       </c>
@@ -8389,7 +8388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>10</v>
       </c>
@@ -8418,7 +8417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>248</v>
       </c>
@@ -8447,7 +8446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>247</v>
       </c>
@@ -8476,7 +8475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>246</v>
       </c>
@@ -8505,7 +8504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>10</v>
       </c>
@@ -8537,7 +8536,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>248</v>
       </c>
@@ -8569,7 +8568,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>247</v>
       </c>
@@ -8601,7 +8600,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>246</v>
       </c>
@@ -8633,7 +8632,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>10</v>
       </c>
@@ -8662,7 +8661,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>248</v>
       </c>
@@ -8691,7 +8690,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>247</v>
       </c>
@@ -8720,7 +8719,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>246</v>
       </c>
@@ -8749,7 +8748,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>10</v>
       </c>
@@ -8778,7 +8777,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>248</v>
       </c>
@@ -8807,7 +8806,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>247</v>
       </c>
@@ -8836,7 +8835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>246</v>
       </c>
@@ -8865,7 +8864,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>10</v>
       </c>
@@ -8897,7 +8896,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>248</v>
       </c>
@@ -8926,7 +8925,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>247</v>
       </c>
@@ -8955,7 +8954,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>246</v>
       </c>
@@ -8987,7 +8986,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -9016,7 +9015,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>248</v>
       </c>
@@ -9045,7 +9044,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>247</v>
       </c>
@@ -9074,7 +9073,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>246</v>
       </c>
@@ -9103,7 +9102,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>10</v>
       </c>
@@ -9132,7 +9131,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>248</v>
       </c>
@@ -9161,7 +9160,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>247</v>
       </c>
@@ -9190,7 +9189,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>246</v>
       </c>
@@ -9222,7 +9221,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>10</v>
       </c>
@@ -9254,7 +9253,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>248</v>
       </c>
@@ -9283,7 +9282,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>247</v>
       </c>
@@ -9312,7 +9311,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>246</v>
       </c>
@@ -9341,7 +9340,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -9370,7 +9369,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>248</v>
       </c>
@@ -9399,7 +9398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>247</v>
       </c>
@@ -9428,7 +9427,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>246</v>
       </c>
@@ -9457,7 +9456,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>10</v>
       </c>
@@ -9489,7 +9488,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>248</v>
       </c>
@@ -9521,7 +9520,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>247</v>
       </c>
@@ -9553,7 +9552,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>246</v>
       </c>
@@ -9585,7 +9584,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>10</v>
       </c>
@@ -9614,7 +9613,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>248</v>
       </c>
@@ -9643,7 +9642,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>247</v>
       </c>
@@ -9672,7 +9671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>246</v>
       </c>
@@ -9701,7 +9700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>10</v>
       </c>
@@ -9730,7 +9729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>248</v>
       </c>
@@ -9759,7 +9758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>247</v>
       </c>
@@ -9788,7 +9787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>246</v>
       </c>
@@ -9817,7 +9816,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>10</v>
       </c>
@@ -9849,7 +9848,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>248</v>
       </c>
@@ -9881,7 +9880,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>247</v>
       </c>
@@ -9913,7 +9912,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>246</v>
       </c>
@@ -9945,7 +9944,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>10</v>
       </c>
@@ -9974,7 +9973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>248</v>
       </c>
@@ -10003,7 +10002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>247</v>
       </c>
@@ -10032,7 +10031,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>246</v>
       </c>
@@ -10061,7 +10060,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>10</v>
       </c>
@@ -10090,7 +10089,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>248</v>
       </c>
@@ -10119,7 +10118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>247</v>
       </c>
@@ -10148,7 +10147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>246</v>
       </c>
@@ -10177,7 +10176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>10</v>
       </c>
@@ -10206,7 +10205,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>248</v>
       </c>
@@ -10235,7 +10234,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>247</v>
       </c>
@@ -10264,7 +10263,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>246</v>
       </c>
@@ -10293,7 +10292,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>10</v>
       </c>
@@ -10325,7 +10324,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>248</v>
       </c>
@@ -10357,7 +10356,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>247</v>
       </c>
@@ -10389,7 +10388,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>246</v>
       </c>
@@ -10421,7 +10420,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>10</v>
       </c>
@@ -10450,7 +10449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>248</v>
       </c>
@@ -10479,7 +10478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>247</v>
       </c>
@@ -10508,7 +10507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>246</v>
       </c>
@@ -10537,7 +10536,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>10</v>
       </c>
@@ -10566,7 +10565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>248</v>
       </c>
@@ -10595,7 +10594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>247</v>
       </c>
@@ -10624,7 +10623,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>246</v>
       </c>
@@ -10653,7 +10652,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>10</v>
       </c>
@@ -10682,7 +10681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>248</v>
       </c>
@@ -10711,7 +10710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>247</v>
       </c>
@@ -10740,7 +10739,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>246</v>
       </c>
@@ -10769,7 +10768,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>10</v>
       </c>
@@ -10801,7 +10800,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>248</v>
       </c>
@@ -10833,7 +10832,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>247</v>
       </c>
@@ -10862,7 +10861,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>246</v>
       </c>
@@ -10891,7 +10890,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>10</v>
       </c>
@@ -10920,7 +10919,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>248</v>
       </c>
@@ -10949,7 +10948,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>247</v>
       </c>
@@ -10978,7 +10977,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>246</v>
       </c>
@@ -11007,7 +11006,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>10</v>
       </c>
@@ -11039,7 +11038,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>248</v>
       </c>
@@ -11071,7 +11070,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>247</v>
       </c>
@@ -11103,7 +11102,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>246</v>
       </c>
@@ -11135,7 +11134,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>10</v>
       </c>
@@ -11167,7 +11166,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>248</v>
       </c>
@@ -11199,7 +11198,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>247</v>
       </c>
@@ -11231,7 +11230,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>246</v>
       </c>
@@ -11263,7 +11262,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>10</v>
       </c>
@@ -11295,7 +11294,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>248</v>
       </c>
@@ -11324,7 +11323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>247</v>
       </c>
@@ -11353,7 +11352,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>246</v>
       </c>
@@ -11382,7 +11381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>10</v>
       </c>
@@ -11411,7 +11410,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>248</v>
       </c>
@@ -11440,7 +11439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>247</v>
       </c>
@@ -11469,7 +11468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>246</v>
       </c>
@@ -11498,7 +11497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>10</v>
       </c>
@@ -11527,7 +11526,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>248</v>
       </c>
@@ -11556,7 +11555,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>247</v>
       </c>
@@ -11585,7 +11584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>246</v>
       </c>
@@ -11614,7 +11613,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>10</v>
       </c>
@@ -11646,7 +11645,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>248</v>
       </c>
@@ -11675,7 +11674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>247</v>
       </c>
@@ -11704,7 +11703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>246</v>
       </c>
@@ -11733,7 +11732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>10</v>
       </c>
@@ -11762,7 +11761,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>248</v>
       </c>
@@ -11791,7 +11790,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>247</v>
       </c>
@@ -11820,7 +11819,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>246</v>
       </c>
@@ -11849,7 +11848,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>10</v>
       </c>
@@ -11878,7 +11877,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>248</v>
       </c>
@@ -11907,7 +11906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>247</v>
       </c>
@@ -11936,7 +11935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>246</v>
       </c>
@@ -11965,7 +11964,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>10</v>
       </c>
@@ -11994,7 +11993,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>248</v>
       </c>
@@ -12023,7 +12022,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>247</v>
       </c>
@@ -12052,7 +12051,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>246</v>
       </c>
@@ -12081,7 +12080,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>10</v>
       </c>
@@ -12113,7 +12112,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>248</v>
       </c>
@@ -12145,7 +12144,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>247</v>
       </c>
@@ -12177,7 +12176,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>246</v>
       </c>
@@ -12209,7 +12208,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>10</v>
       </c>
@@ -12238,7 +12237,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>248</v>
       </c>
@@ -12267,7 +12266,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>247</v>
       </c>
@@ -12296,7 +12295,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>246</v>
       </c>
@@ -12325,7 +12324,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>10</v>
       </c>
@@ -12354,7 +12353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>248</v>
       </c>
@@ -12383,7 +12382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>247</v>
       </c>
@@ -12412,7 +12411,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>246</v>
       </c>
@@ -12441,7 +12440,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>10</v>
       </c>
@@ -12470,7 +12469,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>248</v>
       </c>
@@ -12499,7 +12498,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>247</v>
       </c>
@@ -12528,7 +12527,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>246</v>
       </c>
@@ -12557,7 +12556,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>10</v>
       </c>
@@ -12586,7 +12585,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>248</v>
       </c>
@@ -12618,7 +12617,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>247</v>
       </c>
@@ -12647,7 +12646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>246</v>
       </c>
@@ -12679,7 +12678,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>10</v>
       </c>
@@ -12708,7 +12707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>248</v>
       </c>
@@ -12737,7 +12736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>247</v>
       </c>
@@ -12766,7 +12765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>246</v>
       </c>
@@ -12795,7 +12794,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>10</v>
       </c>
@@ -12824,7 +12823,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>248</v>
       </c>
@@ -12853,7 +12852,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>247</v>
       </c>
@@ -12882,7 +12881,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>246</v>
       </c>
@@ -12911,7 +12910,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>10</v>
       </c>
@@ -12943,7 +12942,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>248</v>
       </c>
@@ -12972,7 +12971,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>247</v>
       </c>
@@ -13001,7 +13000,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>246</v>
       </c>
@@ -13030,7 +13029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>10</v>
       </c>
@@ -13062,7 +13061,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>248</v>
       </c>
@@ -13091,7 +13090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>247</v>
       </c>
@@ -13120,7 +13119,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>246</v>
       </c>
@@ -13149,7 +13148,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>10</v>
       </c>
@@ -13178,7 +13177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>248</v>
       </c>
@@ -13207,7 +13206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>247</v>
       </c>
@@ -13236,7 +13235,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>246</v>
       </c>
@@ -13265,7 +13264,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>10</v>
       </c>
@@ -13297,7 +13296,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>248</v>
       </c>
@@ -13329,7 +13328,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>247</v>
       </c>
@@ -13358,7 +13357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>246</v>
       </c>
@@ -13387,7 +13386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>10</v>
       </c>
@@ -13416,7 +13415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>248</v>
       </c>
@@ -13445,7 +13444,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>247</v>
       </c>
@@ -13474,7 +13473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>246</v>
       </c>
@@ -13503,7 +13502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>10</v>
       </c>
@@ -13535,7 +13534,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>248</v>
       </c>
@@ -13567,7 +13566,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>247</v>
       </c>
@@ -13599,7 +13598,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>246</v>
       </c>
@@ -13631,7 +13630,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>10</v>
       </c>
@@ -13660,7 +13659,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>248</v>
       </c>
@@ -13689,7 +13688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>247</v>
       </c>
@@ -13718,7 +13717,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>246</v>
       </c>
@@ -13750,7 +13749,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>10</v>
       </c>
@@ -13782,7 +13781,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>248</v>
       </c>
@@ -13811,7 +13810,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>247</v>
       </c>
@@ -13840,7 +13839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>246</v>
       </c>
@@ -13869,7 +13868,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>10</v>
       </c>
@@ -13901,7 +13900,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>248</v>
       </c>
@@ -13930,7 +13929,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>247</v>
       </c>
@@ -13959,7 +13958,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>246</v>
       </c>
@@ -13988,7 +13987,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>10</v>
       </c>
@@ -14017,7 +14016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>248</v>
       </c>
@@ -14046,7 +14045,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>247</v>
       </c>
@@ -14075,7 +14074,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>246</v>
       </c>
@@ -14104,7 +14103,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>10</v>
       </c>
@@ -14133,7 +14132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>248</v>
       </c>
@@ -14162,7 +14161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>247</v>
       </c>
@@ -14191,7 +14190,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>246</v>
       </c>
@@ -14220,7 +14219,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>10</v>
       </c>
@@ -14249,7 +14248,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>248</v>
       </c>
@@ -14278,7 +14277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>247</v>
       </c>
@@ -14307,7 +14306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>246</v>
       </c>
@@ -14336,7 +14335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>10</v>
       </c>
@@ -14365,7 +14364,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>248</v>
       </c>
@@ -14394,7 +14393,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>247</v>
       </c>
@@ -14423,7 +14422,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>246</v>
       </c>
@@ -14452,7 +14451,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>10</v>
       </c>
@@ -14475,13 +14474,13 @@
         <v>21</v>
       </c>
       <c r="H426">
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I426">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>248</v>
       </c>
@@ -14504,13 +14503,13 @@
         <v>21</v>
       </c>
       <c r="H427">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I427">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>247</v>
       </c>
@@ -14533,13 +14532,13 @@
         <v>21</v>
       </c>
       <c r="H428">
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I428">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>246</v>
       </c>
@@ -14562,13 +14561,13 @@
         <v>21</v>
       </c>
       <c r="H429">
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I429">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>10</v>
       </c>
@@ -14597,7 +14596,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>248</v>
       </c>
@@ -14626,7 +14625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>247</v>
       </c>
@@ -14655,7 +14654,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>246</v>
       </c>
@@ -14684,7 +14683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>10</v>
       </c>
@@ -14713,7 +14712,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>248</v>
       </c>
@@ -14742,7 +14741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>247</v>
       </c>
@@ -14771,7 +14770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>246</v>
       </c>
@@ -14800,7 +14799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>10</v>
       </c>
@@ -14832,7 +14831,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>248</v>
       </c>
@@ -14864,7 +14863,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>247</v>
       </c>
@@ -14896,7 +14895,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>246</v>
       </c>
@@ -14928,7 +14927,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>10</v>
       </c>
@@ -14957,7 +14956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>248</v>
       </c>
@@ -14986,7 +14985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>247</v>
       </c>
@@ -15015,7 +15014,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>246</v>
       </c>
@@ -15044,7 +15043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>10</v>
       </c>
@@ -15073,7 +15072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>248</v>
       </c>
@@ -15102,7 +15101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>247</v>
       </c>
@@ -15131,7 +15130,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>246</v>
       </c>
@@ -15160,7 +15159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>10</v>
       </c>
@@ -15189,7 +15188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>248</v>
       </c>
@@ -15218,7 +15217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>247</v>
       </c>
@@ -15247,7 +15246,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>246</v>
       </c>
@@ -15276,7 +15275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>10</v>
       </c>
@@ -15305,7 +15304,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>248</v>
       </c>
@@ -15334,7 +15333,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>247</v>
       </c>
@@ -15363,7 +15362,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>246</v>
       </c>
@@ -15392,7 +15391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>10</v>
       </c>
@@ -15421,7 +15420,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>248</v>
       </c>
@@ -15450,7 +15449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>247</v>
       </c>
@@ -15479,7 +15478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>246</v>
       </c>
@@ -15511,7 +15510,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>10</v>
       </c>
@@ -15540,7 +15539,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>248</v>
       </c>
@@ -15569,7 +15568,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>247</v>
       </c>
@@ -15601,7 +15600,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>246</v>
       </c>
@@ -15630,7 +15629,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>10</v>
       </c>
@@ -15659,7 +15658,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>248</v>
       </c>
@@ -15688,7 +15687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>247</v>
       </c>
@@ -15717,7 +15716,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>246</v>
       </c>
@@ -15746,7 +15745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>10</v>
       </c>
@@ -15775,7 +15774,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>248</v>
       </c>
@@ -15804,7 +15803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>247</v>
       </c>
@@ -15833,7 +15832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>246</v>
       </c>
@@ -15862,7 +15861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>10</v>
       </c>
@@ -15891,7 +15890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>248</v>
       </c>
@@ -15920,7 +15919,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>247</v>
       </c>
@@ -15949,7 +15948,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>246</v>
       </c>
@@ -15978,7 +15977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>10</v>
       </c>
@@ -16007,7 +16006,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>248</v>
       </c>
@@ -16036,7 +16035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>247</v>
       </c>
@@ -16065,7 +16064,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>246</v>
       </c>
@@ -16094,7 +16093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>10</v>
       </c>
@@ -16123,7 +16122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>248</v>
       </c>
@@ -16152,7 +16151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>247</v>
       </c>
@@ -16181,7 +16180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>246</v>
       </c>
@@ -16210,7 +16209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>10</v>
       </c>
@@ -16239,7 +16238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>248</v>
       </c>
@@ -16268,7 +16267,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>247</v>
       </c>
@@ -16297,7 +16296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>246</v>
       </c>
@@ -16326,7 +16325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>10</v>
       </c>
@@ -16355,7 +16354,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>248</v>
       </c>
@@ -16384,7 +16383,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>247</v>
       </c>
@@ -16413,7 +16412,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>246</v>
       </c>
@@ -16442,7 +16441,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>10</v>
       </c>
@@ -16471,7 +16470,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>248</v>
       </c>
@@ -16500,7 +16499,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>247</v>
       </c>
@@ -16529,7 +16528,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>246</v>
       </c>
@@ -16558,7 +16557,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>10</v>
       </c>
@@ -16587,7 +16586,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>248</v>
       </c>
@@ -16616,7 +16615,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>247</v>
       </c>
@@ -16645,7 +16644,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>246</v>
       </c>
@@ -16674,7 +16673,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>10</v>
       </c>
@@ -16703,7 +16702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>248</v>
       </c>
@@ -16732,7 +16731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>247</v>
       </c>
@@ -16761,7 +16760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>246</v>
       </c>
@@ -16790,7 +16789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>10</v>
       </c>
@@ -16819,7 +16818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>248</v>
       </c>
@@ -16848,7 +16847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>247</v>
       </c>
@@ -16877,7 +16876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>246</v>
       </c>
@@ -16906,7 +16905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>10</v>
       </c>
@@ -16935,7 +16934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>248</v>
       </c>
@@ -16964,7 +16963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>247</v>
       </c>
@@ -16993,7 +16992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>246</v>
       </c>
@@ -17022,7 +17021,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>10</v>
       </c>
@@ -17054,7 +17053,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>248</v>
       </c>
@@ -17086,7 +17085,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>247</v>
       </c>
@@ -17118,7 +17117,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>246</v>
       </c>
@@ -17150,7 +17149,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>10</v>
       </c>
@@ -17182,7 +17181,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>248</v>
       </c>
@@ -17214,7 +17213,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>247</v>
       </c>
@@ -17246,7 +17245,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="521" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>246</v>
       </c>
@@ -17278,7 +17277,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>10</v>
       </c>
@@ -17307,7 +17306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>248</v>
       </c>
@@ -17336,7 +17335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>247</v>
       </c>
@@ -17365,7 +17364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>246</v>
       </c>
@@ -17394,7 +17393,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>10</v>
       </c>
@@ -17423,7 +17422,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>248</v>
       </c>
@@ -17452,7 +17451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="528" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>247</v>
       </c>
@@ -17481,7 +17480,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>246</v>
       </c>
@@ -17510,7 +17509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>10</v>
       </c>
@@ -17539,7 +17538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>248</v>
       </c>
@@ -17568,7 +17567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>247</v>
       </c>
@@ -17597,7 +17596,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>246</v>
       </c>
@@ -17626,7 +17625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>10</v>
       </c>
@@ -17655,7 +17654,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>248</v>
       </c>
@@ -17684,7 +17683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>247</v>
       </c>
@@ -17713,7 +17712,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>246</v>
       </c>
@@ -17742,7 +17741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>10</v>
       </c>
@@ -17771,7 +17770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>248</v>
       </c>
@@ -17800,7 +17799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>247</v>
       </c>
@@ -17829,7 +17828,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>246</v>
       </c>
@@ -17858,7 +17857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>10</v>
       </c>
@@ -17887,7 +17886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>248</v>
       </c>
@@ -17916,7 +17915,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>247</v>
       </c>
@@ -17945,7 +17944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>246</v>
       </c>
@@ -17974,7 +17973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>10</v>
       </c>
@@ -18003,7 +18002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>248</v>
       </c>
@@ -18032,7 +18031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>247</v>
       </c>
@@ -18061,7 +18060,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>246</v>
       </c>
@@ -18090,7 +18089,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>10</v>
       </c>
@@ -18119,7 +18118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>248</v>
       </c>
@@ -18148,7 +18147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>247</v>
       </c>
@@ -18177,7 +18176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>246</v>
       </c>
@@ -18206,7 +18205,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>10</v>
       </c>
@@ -18235,7 +18234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>248</v>
       </c>
@@ -18264,7 +18263,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>247</v>
       </c>
@@ -18293,7 +18292,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>246</v>
       </c>
@@ -18325,7 +18324,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>10</v>
       </c>
@@ -18354,7 +18353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>248</v>
       </c>
@@ -18383,7 +18382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>247</v>
       </c>
@@ -18412,7 +18411,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>246</v>
       </c>
@@ -18441,7 +18440,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>10</v>
       </c>
@@ -18470,7 +18469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>248</v>
       </c>
@@ -18499,7 +18498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>247</v>
       </c>
@@ -18528,7 +18527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>246</v>
       </c>
@@ -18557,7 +18556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>10</v>
       </c>
@@ -18586,7 +18585,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>248</v>
       </c>
@@ -18615,7 +18614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>247</v>
       </c>
@@ -18644,7 +18643,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>246</v>
       </c>
@@ -18673,7 +18672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>10</v>
       </c>
@@ -18702,7 +18701,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>248</v>
       </c>
@@ -18731,7 +18730,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>247</v>
       </c>
@@ -18760,7 +18759,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>246</v>
       </c>
@@ -18789,7 +18788,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>10</v>
       </c>
@@ -18818,7 +18817,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>248</v>
       </c>
@@ -18847,7 +18846,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>247</v>
       </c>
@@ -18876,7 +18875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>246</v>
       </c>
@@ -18905,7 +18904,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>10</v>
       </c>
@@ -18934,7 +18933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>248</v>
       </c>
@@ -18963,7 +18962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>247</v>
       </c>
@@ -18992,7 +18991,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>246</v>
       </c>
@@ -19021,7 +19020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>10</v>
       </c>
@@ -19050,7 +19049,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>248</v>
       </c>
@@ -19079,7 +19078,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>247</v>
       </c>
@@ -19108,7 +19107,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>246</v>
       </c>
@@ -19137,7 +19136,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>10</v>
       </c>
@@ -19166,7 +19165,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>248</v>
       </c>
@@ -19195,7 +19194,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>247</v>
       </c>
@@ -19224,7 +19223,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>246</v>
       </c>
@@ -19253,7 +19252,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>10</v>
       </c>
@@ -19282,7 +19281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>248</v>
       </c>
@@ -19311,7 +19310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>247</v>
       </c>
@@ -19340,7 +19339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>246</v>
       </c>
@@ -19369,7 +19368,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>10</v>
       </c>
@@ -19398,7 +19397,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>248</v>
       </c>
@@ -19427,7 +19426,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>247</v>
       </c>
@@ -19456,7 +19455,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>246</v>
       </c>
@@ -19485,7 +19484,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>10</v>
       </c>
@@ -19514,7 +19513,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>248</v>
       </c>
@@ -19546,7 +19545,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>247</v>
       </c>
@@ -19575,7 +19574,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>246</v>
       </c>
@@ -19604,7 +19603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>10</v>
       </c>
@@ -19633,7 +19632,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>248</v>
       </c>
@@ -19662,7 +19661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>247</v>
       </c>
@@ -19691,7 +19690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>246</v>
       </c>
@@ -19720,7 +19719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>10</v>
       </c>
@@ -19749,7 +19748,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>248</v>
       </c>
@@ -19778,7 +19777,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>247</v>
       </c>
@@ -19807,7 +19806,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>246</v>
       </c>
@@ -19836,7 +19835,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>10</v>
       </c>
@@ -19865,7 +19864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>248</v>
       </c>
@@ -19894,7 +19893,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>247</v>
       </c>
@@ -19923,7 +19922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>246</v>
       </c>
@@ -19952,7 +19951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>10</v>
       </c>
@@ -19981,7 +19980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>248</v>
       </c>
@@ -20010,7 +20009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>247</v>
       </c>
@@ -20039,7 +20038,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>246</v>
       </c>
@@ -20068,7 +20067,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>10</v>
       </c>
@@ -20097,7 +20096,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>248</v>
       </c>
@@ -20126,7 +20125,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>247</v>
       </c>
@@ -20155,7 +20154,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>246</v>
       </c>
@@ -20184,7 +20183,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>10</v>
       </c>
@@ -20213,7 +20212,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>248</v>
       </c>
@@ -20242,7 +20241,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>247</v>
       </c>
@@ -20271,7 +20270,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="625" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>246</v>
       </c>
@@ -20300,7 +20299,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="626" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>10</v>
       </c>
@@ -20329,7 +20328,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="627" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>248</v>
       </c>
@@ -20358,7 +20357,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="628" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>247</v>
       </c>
@@ -20387,7 +20386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="629" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>246</v>
       </c>
@@ -20416,7 +20415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="630" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>10</v>
       </c>
@@ -20445,7 +20444,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="631" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>248</v>
       </c>
@@ -20474,7 +20473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="632" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>247</v>
       </c>
@@ -20503,7 +20502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="633" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>246</v>
       </c>
@@ -20532,7 +20531,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="634" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>10</v>
       </c>
@@ -20561,7 +20560,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="635" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>248</v>
       </c>
@@ -20590,7 +20589,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="636" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>247</v>
       </c>
@@ -20622,7 +20621,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="637" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>246</v>
       </c>
@@ -20651,7 +20650,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="638" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>10</v>
       </c>
@@ -20680,7 +20679,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="639" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>248</v>
       </c>
@@ -20709,7 +20708,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="640" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>247</v>
       </c>
@@ -20738,7 +20737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="641" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>246</v>
       </c>
@@ -20767,7 +20766,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="642" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>10</v>
       </c>
@@ -20796,7 +20795,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="643" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>248</v>
       </c>
@@ -20825,7 +20824,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="644" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>247</v>
       </c>
@@ -20854,7 +20853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="645" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>246</v>
       </c>
@@ -20883,7 +20882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="646" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>10</v>
       </c>
@@ -20915,7 +20914,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="647" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>248</v>
       </c>
@@ -20947,7 +20946,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="648" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>247</v>
       </c>
@@ -20979,7 +20978,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="649" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>246</v>
       </c>
@@ -21011,7 +21010,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="650" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>10</v>
       </c>
@@ -21040,7 +21039,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="651" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>248</v>
       </c>
@@ -21069,7 +21068,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="652" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>247</v>
       </c>
@@ -21098,7 +21097,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="653" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>246</v>
       </c>
@@ -21127,7 +21126,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="654" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>10</v>
       </c>
@@ -21156,7 +21155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="655" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>248</v>
       </c>
@@ -21185,7 +21184,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="656" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>247</v>
       </c>
@@ -21214,7 +21213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>246</v>
       </c>
@@ -21243,7 +21242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>10</v>
       </c>
@@ -21272,7 +21271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>248</v>
       </c>
@@ -21301,7 +21300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>247</v>
       </c>
@@ -21330,7 +21329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>246</v>
       </c>
@@ -21359,7 +21358,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>10</v>
       </c>
@@ -21388,7 +21387,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>248</v>
       </c>
@@ -21417,7 +21416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>247</v>
       </c>
@@ -21446,7 +21445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>246</v>
       </c>
@@ -21475,7 +21474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>10</v>
       </c>
@@ -21504,7 +21503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>248</v>
       </c>
@@ -21533,7 +21532,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>247</v>
       </c>
@@ -21562,7 +21561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>246</v>
       </c>
@@ -21591,7 +21590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>10</v>
       </c>
@@ -21620,7 +21619,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>248</v>
       </c>
@@ -21649,7 +21648,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>247</v>
       </c>
@@ -21678,7 +21677,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="673" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>246</v>
       </c>
@@ -21710,7 +21709,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="674" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>10</v>
       </c>
@@ -21739,7 +21738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="675" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>248</v>
       </c>
@@ -21768,7 +21767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="676" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>247</v>
       </c>
@@ -21797,7 +21796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="677" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>246</v>
       </c>
@@ -21826,7 +21825,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="678" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>10</v>
       </c>
@@ -21855,7 +21854,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="679" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>248</v>
       </c>
@@ -21884,7 +21883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="680" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>247</v>
       </c>
@@ -21913,7 +21912,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="681" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>246</v>
       </c>
@@ -21942,7 +21941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="682" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>10</v>
       </c>
@@ -21971,7 +21970,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="683" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>248</v>
       </c>
@@ -22000,7 +21999,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="684" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>247</v>
       </c>
@@ -22029,7 +22028,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="685" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>246</v>
       </c>
@@ -22058,7 +22057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="686" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>10</v>
       </c>
@@ -22087,7 +22086,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="687" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>248</v>
       </c>
@@ -22116,7 +22115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="688" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>247</v>
       </c>
@@ -22145,7 +22144,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>246</v>
       </c>
@@ -22174,7 +22173,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>10</v>
       </c>
@@ -22203,7 +22202,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>248</v>
       </c>
@@ -22232,7 +22231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>247</v>
       </c>
@@ -22261,7 +22260,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>246</v>
       </c>
@@ -22290,7 +22289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>10</v>
       </c>
@@ -22319,7 +22318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>248</v>
       </c>
@@ -22348,7 +22347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>247</v>
       </c>
@@ -22377,7 +22376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>246</v>
       </c>
@@ -22406,7 +22405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>10</v>
       </c>
@@ -22435,7 +22434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>248</v>
       </c>
@@ -22464,7 +22463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>247</v>
       </c>
@@ -22493,7 +22492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>246</v>
       </c>
@@ -22522,7 +22521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>10</v>
       </c>
@@ -22551,7 +22550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>248</v>
       </c>
@@ -22580,7 +22579,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>247</v>
       </c>
@@ -22609,7 +22608,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>246</v>
       </c>
@@ -22638,7 +22637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>10</v>
       </c>
@@ -22667,7 +22666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>248</v>
       </c>
@@ -22696,7 +22695,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>247</v>
       </c>
@@ -22725,7 +22724,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>246</v>
       </c>
@@ -22754,7 +22753,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>10</v>
       </c>
@@ -22783,7 +22782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>248</v>
       </c>
@@ -22812,7 +22811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>247</v>
       </c>
@@ -22841,7 +22840,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>246</v>
       </c>
@@ -22870,7 +22869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>10</v>
       </c>
@@ -22899,7 +22898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>248</v>
       </c>
@@ -22928,7 +22927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>247</v>
       </c>
@@ -22957,7 +22956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>246</v>
       </c>
@@ -22986,7 +22985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>10</v>
       </c>
@@ -23015,7 +23014,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>248</v>
       </c>
@@ -23044,7 +23043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>247</v>
       </c>
@@ -23073,7 +23072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>246</v>
       </c>
@@ -23102,7 +23101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>10</v>
       </c>
@@ -23131,7 +23130,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>248</v>
       </c>
@@ -23160,7 +23159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>247</v>
       </c>
@@ -23189,7 +23188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>246</v>
       </c>
@@ -23218,7 +23217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>10</v>
       </c>
@@ -23247,7 +23246,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>248</v>
       </c>
@@ -23276,7 +23275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>247</v>
       </c>
@@ -23305,7 +23304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>246</v>
       </c>
@@ -23334,7 +23333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>10</v>
       </c>
@@ -23363,7 +23362,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>248</v>
       </c>
@@ -23392,7 +23391,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>247</v>
       </c>
@@ -23421,7 +23420,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>246</v>
       </c>
@@ -23453,7 +23452,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>10</v>
       </c>
@@ -23482,7 +23481,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>248</v>
       </c>
@@ -23511,7 +23510,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>247</v>
       </c>
@@ -23540,7 +23539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>246</v>
       </c>
@@ -23569,7 +23568,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>10</v>
       </c>
@@ -23598,7 +23597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>248</v>
       </c>
@@ -23627,7 +23626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>247</v>
       </c>
@@ -23656,7 +23655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>246</v>
       </c>
@@ -23685,7 +23684,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>10</v>
       </c>
@@ -23714,7 +23713,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>248</v>
       </c>
@@ -23743,7 +23742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>247</v>
       </c>
@@ -23772,7 +23771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>246</v>
       </c>
@@ -23801,7 +23800,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>10</v>
       </c>
@@ -23830,7 +23829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>248</v>
       </c>
@@ -23859,7 +23858,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>247</v>
       </c>
@@ -23888,7 +23887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>246</v>
       </c>
@@ -23917,7 +23916,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>10</v>
       </c>
@@ -23946,7 +23945,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>248</v>
       </c>
@@ -23975,7 +23974,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>247</v>
       </c>
@@ -24004,7 +24003,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>246</v>
       </c>
@@ -24033,7 +24032,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="754" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>10</v>
       </c>
@@ -24062,7 +24061,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>248</v>
       </c>
@@ -24091,7 +24090,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>247</v>
       </c>
@@ -24120,7 +24119,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="757" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>246</v>
       </c>
@@ -24149,7 +24148,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>10</v>
       </c>
@@ -24181,7 +24180,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>248</v>
       </c>
@@ -24210,7 +24209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="760" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>247</v>
       </c>
@@ -24239,7 +24238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>246</v>
       </c>
@@ -24268,7 +24267,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>10</v>
       </c>
@@ -24300,7 +24299,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="763" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>248</v>
       </c>
@@ -24332,7 +24331,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="764" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>247</v>
       </c>
@@ -24361,7 +24360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="765" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>246</v>
       </c>
@@ -24390,7 +24389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="766" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>10</v>
       </c>
@@ -24419,7 +24418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="767" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>248</v>
       </c>
@@ -24448,7 +24447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="768" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>247</v>
       </c>
@@ -24477,7 +24476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="769" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>246</v>
       </c>
@@ -24506,7 +24505,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="770" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>10</v>
       </c>
@@ -24535,7 +24534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="771" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>248</v>
       </c>
@@ -24564,7 +24563,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="772" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>247</v>
       </c>
@@ -24593,7 +24592,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="773" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>246</v>
       </c>
@@ -24622,7 +24621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="774" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>10</v>
       </c>
@@ -24654,7 +24653,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="775" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>248</v>
       </c>
@@ -24683,7 +24682,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="776" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>247</v>
       </c>
@@ -24712,7 +24711,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="777" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>246</v>
       </c>
@@ -24741,7 +24740,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="778" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>10</v>
       </c>
@@ -24770,7 +24769,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="779" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>248</v>
       </c>
@@ -24799,7 +24798,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="780" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>247</v>
       </c>
@@ -24828,7 +24827,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="781" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>246</v>
       </c>
@@ -24857,7 +24856,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="782" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>10</v>
       </c>
@@ -24886,7 +24885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="783" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>248</v>
       </c>
@@ -24915,7 +24914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="784" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>247</v>
       </c>
@@ -24944,7 +24943,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>246</v>
       </c>
@@ -24973,7 +24972,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>10</v>
       </c>
@@ -25002,7 +25001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>248</v>
       </c>
@@ -25031,7 +25030,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>247</v>
       </c>
@@ -25060,7 +25059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>246</v>
       </c>
@@ -25089,7 +25088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>10</v>
       </c>
@@ -25118,7 +25117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>248</v>
       </c>
@@ -25147,7 +25146,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>247</v>
       </c>
@@ -25176,7 +25175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>246</v>
       </c>
@@ -25205,7 +25204,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>10</v>
       </c>
@@ -25234,7 +25233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>248</v>
       </c>
@@ -25263,7 +25262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>247</v>
       </c>
@@ -25292,7 +25291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>246</v>
       </c>
@@ -25321,7 +25320,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>10</v>
       </c>
@@ -25350,7 +25349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>248</v>
       </c>
@@ -25379,7 +25378,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>247</v>
       </c>
@@ -25408,7 +25407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="801" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>246</v>
       </c>
@@ -25437,7 +25436,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="802" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>10</v>
       </c>
@@ -25466,7 +25465,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="803" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>248</v>
       </c>
@@ -25495,7 +25494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="804" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>247</v>
       </c>
@@ -25524,7 +25523,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="805" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>246</v>
       </c>
@@ -25553,7 +25552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="806" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>10</v>
       </c>
@@ -25585,7 +25584,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="807" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>248</v>
       </c>
@@ -25614,7 +25613,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="808" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>247</v>
       </c>
@@ -25643,7 +25642,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="809" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>246</v>
       </c>
@@ -25675,7 +25674,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="810" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>10</v>
       </c>
@@ -25704,7 +25703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="811" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>248</v>
       </c>
@@ -25733,7 +25732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="812" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>247</v>
       </c>
@@ -25762,7 +25761,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="813" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>246</v>
       </c>
@@ -25791,7 +25790,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="814" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>10</v>
       </c>
@@ -25820,7 +25819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="815" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>248</v>
       </c>
@@ -25849,7 +25848,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="816" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>247</v>
       </c>
@@ -25878,7 +25877,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>246</v>
       </c>
@@ -25907,7 +25906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>10</v>
       </c>
@@ -25936,7 +25935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>248</v>
       </c>
@@ -25965,7 +25964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>247</v>
       </c>
@@ -25994,7 +25993,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>246</v>
       </c>
@@ -26023,7 +26022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>10</v>
       </c>
@@ -26052,7 +26051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>248</v>
       </c>
@@ -26081,7 +26080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>247</v>
       </c>
@@ -26110,7 +26109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>246</v>
       </c>
@@ -26139,7 +26138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>10</v>
       </c>
@@ -26168,7 +26167,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>248</v>
       </c>
@@ -26197,7 +26196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>247</v>
       </c>
@@ -26226,7 +26225,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>246</v>
       </c>
@@ -26255,7 +26254,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>10</v>
       </c>
@@ -26284,7 +26283,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>248</v>
       </c>
@@ -26313,7 +26312,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>247</v>
       </c>
@@ -26342,7 +26341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="833" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>246</v>
       </c>
@@ -26371,7 +26370,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="834" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>10</v>
       </c>
@@ -26400,7 +26399,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="835" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>248</v>
       </c>
@@ -26429,7 +26428,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="836" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>247</v>
       </c>
@@ -26458,7 +26457,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="837" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>246</v>
       </c>
@@ -26490,7 +26489,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="838" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>10</v>
       </c>
@@ -26519,7 +26518,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="839" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>248</v>
       </c>
@@ -26548,7 +26547,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="840" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>247</v>
       </c>
@@ -26577,7 +26576,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="841" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>246</v>
       </c>
@@ -26606,7 +26605,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="842" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>10</v>
       </c>
@@ -26635,7 +26634,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="843" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>248</v>
       </c>
@@ -26664,7 +26663,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="844" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>247</v>
       </c>
@@ -26693,7 +26692,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="845" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>246</v>
       </c>
@@ -26722,7 +26721,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="846" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>10</v>
       </c>
@@ -26751,7 +26750,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="847" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>248</v>
       </c>
@@ -26780,7 +26779,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="848" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>247</v>
       </c>
@@ -26809,7 +26808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>246</v>
       </c>
@@ -26838,7 +26837,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>10</v>
       </c>
@@ -26867,7 +26866,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>248</v>
       </c>
@@ -26896,7 +26895,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>247</v>
       </c>
@@ -26925,7 +26924,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>246</v>
       </c>
@@ -26954,7 +26953,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>10</v>
       </c>
@@ -26983,7 +26982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>248</v>
       </c>
@@ -27012,7 +27011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>247</v>
       </c>
@@ -27041,7 +27040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>246</v>
       </c>
@@ -27070,7 +27069,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>10</v>
       </c>
@@ -27099,7 +27098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>248</v>
       </c>
@@ -27128,7 +27127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>247</v>
       </c>
@@ -27157,7 +27156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>246</v>
       </c>
@@ -27186,7 +27185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>10</v>
       </c>
@@ -27215,7 +27214,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>248</v>
       </c>
@@ -27244,7 +27243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>247</v>
       </c>
@@ -27273,7 +27272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>246</v>
       </c>
@@ -27302,7 +27301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>10</v>
       </c>
@@ -27331,7 +27330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>248</v>
       </c>
@@ -27360,7 +27359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>247</v>
       </c>
@@ -27389,7 +27388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>246</v>
       </c>
@@ -27418,7 +27417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>10</v>
       </c>
@@ -27447,7 +27446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>248</v>
       </c>
@@ -27476,7 +27475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>247</v>
       </c>
@@ -27505,7 +27504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>246</v>
       </c>
@@ -27534,7 +27533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>10</v>
       </c>
@@ -27563,7 +27562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>248</v>
       </c>
@@ -27592,7 +27591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>247</v>
       </c>
@@ -27621,7 +27620,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>246</v>
       </c>
@@ -27650,7 +27649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>10</v>
       </c>
@@ -27679,7 +27678,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>248</v>
       </c>
@@ -27708,7 +27707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>247</v>
       </c>
@@ -27737,7 +27736,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>246</v>
       </c>
@@ -27766,7 +27765,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>10</v>
       </c>
@@ -27795,7 +27794,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>248</v>
       </c>
@@ -27824,7 +27823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>247</v>
       </c>
@@ -27853,7 +27852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>246</v>
       </c>
@@ -27882,7 +27881,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>10</v>
       </c>
@@ -27911,7 +27910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>248</v>
       </c>
@@ -27940,7 +27939,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>247</v>
       </c>
@@ -27969,7 +27968,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>246</v>
       </c>
@@ -27998,7 +27997,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>10</v>
       </c>
@@ -28027,7 +28026,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>248</v>
       </c>
@@ -28056,7 +28055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>247</v>
       </c>
@@ -28085,7 +28084,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>246</v>
       </c>
@@ -28114,7 +28113,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>10</v>
       </c>
@@ -28143,7 +28142,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>248</v>
       </c>
@@ -28172,7 +28171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>247</v>
       </c>
@@ -28201,7 +28200,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="897" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>246</v>
       </c>
@@ -28230,7 +28229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="898" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>10</v>
       </c>
@@ -28259,7 +28258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="899" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>248</v>
       </c>
@@ -28288,7 +28287,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="900" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>247</v>
       </c>
@@ -28317,7 +28316,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="901" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>246</v>
       </c>
@@ -28346,7 +28345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="902" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>10</v>
       </c>
@@ -28375,7 +28374,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="903" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>248</v>
       </c>
@@ -28404,7 +28403,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="904" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>247</v>
       </c>
@@ -28433,7 +28432,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="905" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>246</v>
       </c>
@@ -28462,7 +28461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="906" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>10</v>
       </c>
@@ -28494,7 +28493,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="907" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>248</v>
       </c>
@@ -28523,7 +28522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="908" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>247</v>
       </c>
@@ -28552,7 +28551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="909" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>246</v>
       </c>
@@ -28581,7 +28580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="910" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>10</v>
       </c>
@@ -28613,7 +28612,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="911" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>248</v>
       </c>
@@ -28642,7 +28641,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="912" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>247</v>
       </c>
@@ -28671,7 +28670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="913" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>246</v>
       </c>
@@ -28703,7 +28702,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="914" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>10</v>
       </c>
@@ -28732,7 +28731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="915" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>248</v>
       </c>
@@ -28761,7 +28760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="916" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>247</v>
       </c>
@@ -28790,7 +28789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="917" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>246</v>
       </c>
@@ -28819,7 +28818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="918" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>10</v>
       </c>
@@ -28848,7 +28847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="919" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>248</v>
       </c>
@@ -28877,7 +28876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="920" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>247</v>
       </c>
@@ -28906,7 +28905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="921" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>246</v>
       </c>
@@ -28935,7 +28934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="922" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>10</v>
       </c>
@@ -28964,7 +28963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="923" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>248</v>
       </c>
@@ -28993,7 +28992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="924" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>247</v>
       </c>
@@ -29022,7 +29021,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="925" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>246</v>
       </c>
@@ -29051,7 +29050,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="926" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>10</v>
       </c>
@@ -29080,7 +29079,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="927" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>248</v>
       </c>
@@ -29109,7 +29108,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="928" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>247</v>
       </c>
@@ -29138,7 +29137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="929" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>246</v>
       </c>
@@ -29167,7 +29166,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="930" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>10</v>
       </c>
@@ -29196,7 +29195,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="931" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>248</v>
       </c>
@@ -29225,7 +29224,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="932" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>247</v>
       </c>
@@ -29254,7 +29253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="933" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>246</v>
       </c>
@@ -29283,7 +29282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="934" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>10</v>
       </c>
@@ -29312,7 +29311,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="935" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>248</v>
       </c>
@@ -29341,7 +29340,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="936" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>247</v>
       </c>
@@ -29370,7 +29369,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="937" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>246</v>
       </c>
@@ -29399,7 +29398,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="938" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>10</v>
       </c>
@@ -29428,7 +29427,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="939" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>248</v>
       </c>
@@ -29457,7 +29456,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="940" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>247</v>
       </c>
@@ -29486,7 +29485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="941" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>246</v>
       </c>
@@ -29515,7 +29514,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="942" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>10</v>
       </c>
@@ -29544,7 +29543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="943" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>248</v>
       </c>
@@ -29573,7 +29572,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="944" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>247</v>
       </c>
@@ -29602,7 +29601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="945" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="945" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>246</v>
       </c>
@@ -29631,7 +29630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="946" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>10</v>
       </c>
@@ -29660,7 +29659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="947" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>248</v>
       </c>
@@ -29689,7 +29688,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="948" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>247</v>
       </c>
@@ -29718,7 +29717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="949" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>246</v>
       </c>
@@ -29747,7 +29746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="950" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>10</v>
       </c>
@@ -29776,7 +29775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="951" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>248</v>
       </c>
@@ -29805,7 +29804,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="952" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>247</v>
       </c>
@@ -29834,7 +29833,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="953" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>246</v>
       </c>
@@ -29866,7 +29865,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="954" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>10</v>
       </c>
@@ -29895,7 +29894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="955" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>248</v>
       </c>
@@ -29924,7 +29923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="956" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>247</v>
       </c>
@@ -29953,7 +29952,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="957" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>246</v>
       </c>
@@ -29982,7 +29981,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="958" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>10</v>
       </c>
@@ -30011,7 +30010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="959" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>248</v>
       </c>
@@ -30040,7 +30039,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="960" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>247</v>
       </c>
@@ -30069,7 +30068,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="961" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>246</v>
       </c>
@@ -30098,7 +30097,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="962" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>10</v>
       </c>
@@ -30127,7 +30126,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="963" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>248</v>
       </c>
@@ -30156,7 +30155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="964" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>247</v>
       </c>
@@ -30185,7 +30184,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="965" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>246</v>
       </c>
@@ -30214,7 +30213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="966" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>10</v>
       </c>
@@ -30243,7 +30242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="967" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>248</v>
       </c>
@@ -30272,7 +30271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="968" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>247</v>
       </c>
@@ -30301,7 +30300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="969" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>246</v>
       </c>
@@ -30330,7 +30329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="970" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>10</v>
       </c>
@@ -30359,7 +30358,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="971" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>248</v>
       </c>
@@ -30388,7 +30387,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="972" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>247</v>
       </c>
@@ -30417,7 +30416,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="973" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>246</v>
       </c>
@@ -30446,7 +30445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="974" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>10</v>
       </c>
@@ -30475,7 +30474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="975" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>248</v>
       </c>
@@ -30504,7 +30503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="976" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>247</v>
       </c>
@@ -30533,7 +30532,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="977" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>246</v>
       </c>
@@ -30562,7 +30561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="978" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>10</v>
       </c>
@@ -30591,7 +30590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="979" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>248</v>
       </c>
@@ -30620,7 +30619,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="980" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>247</v>
       </c>
@@ -30649,7 +30648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="981" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>246</v>
       </c>
@@ -30678,7 +30677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="982" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>10</v>
       </c>
@@ -30707,7 +30706,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="983" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>248</v>
       </c>
@@ -30736,7 +30735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="984" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>247</v>
       </c>
@@ -30765,7 +30764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="985" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>246</v>
       </c>
@@ -30794,7 +30793,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="986" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>10</v>
       </c>
@@ -30823,7 +30822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="987" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>248</v>
       </c>
@@ -30852,7 +30851,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="988" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>247</v>
       </c>
@@ -30881,7 +30880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="989" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>246</v>
       </c>
@@ -30910,7 +30909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="990" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>10</v>
       </c>
@@ -30939,7 +30938,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="991" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>248</v>
       </c>
@@ -30968,7 +30967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="992" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>247</v>
       </c>
@@ -30997,7 +30996,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="993" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>246</v>
       </c>
@@ -31026,7 +31025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="994" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>10</v>
       </c>
@@ -31055,7 +31054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="995" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>248</v>
       </c>
@@ -31084,7 +31083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="996" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>247</v>
       </c>
@@ -31113,7 +31112,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="997" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>246</v>
       </c>
@@ -31142,7 +31141,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="998" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>10</v>
       </c>
@@ -31171,7 +31170,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="999" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>248</v>
       </c>
@@ -31200,7 +31199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>247</v>
       </c>
@@ -31229,7 +31228,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>246</v>
       </c>
@@ -31258,7 +31257,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>10</v>
       </c>
@@ -31287,7 +31286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>248</v>
       </c>
@@ -31316,7 +31315,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>247</v>
       </c>
@@ -31345,7 +31344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>246</v>
       </c>
@@ -31374,7 +31373,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>10</v>
       </c>
@@ -31403,7 +31402,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>248</v>
       </c>
@@ -31432,7 +31431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>247</v>
       </c>
@@ -31461,7 +31460,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>246</v>
       </c>
@@ -31490,7 +31489,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>10</v>
       </c>
@@ -31519,7 +31518,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>248</v>
       </c>
@@ -31548,7 +31547,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>247</v>
       </c>
@@ -31577,7 +31576,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>246</v>
       </c>
@@ -31606,7 +31605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>10</v>
       </c>
@@ -31635,7 +31634,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>248</v>
       </c>
@@ -31664,7 +31663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>247</v>
       </c>
@@ -31693,7 +31692,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>246</v>
       </c>
@@ -31722,7 +31721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>10</v>
       </c>
@@ -31751,7 +31750,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>248</v>
       </c>
@@ -31780,7 +31779,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>247</v>
       </c>
@@ -31809,7 +31808,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>246</v>
       </c>
@@ -31838,7 +31837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>10</v>
       </c>
@@ -31867,7 +31866,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>248</v>
       </c>
@@ -31896,7 +31895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>247</v>
       </c>
@@ -31925,7 +31924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>246</v>
       </c>
@@ -31954,7 +31953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>10</v>
       </c>
@@ -31983,7 +31982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>248</v>
       </c>
@@ -32012,7 +32011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>247</v>
       </c>
@@ -32041,7 +32040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>246</v>
       </c>
@@ -32070,7 +32069,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>10</v>
       </c>
@@ -32099,7 +32098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>248</v>
       </c>
@@ -32128,7 +32127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>247</v>
       </c>
@@ -32157,7 +32156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>246</v>
       </c>
@@ -32186,7 +32185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>10</v>
       </c>
@@ -32215,7 +32214,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>248</v>
       </c>
@@ -32244,7 +32243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>247</v>
       </c>
@@ -32273,7 +32272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>246</v>
       </c>
@@ -32302,7 +32301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>10</v>
       </c>
@@ -32331,7 +32330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>248</v>
       </c>
@@ -32360,7 +32359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>247</v>
       </c>
@@ -32389,7 +32388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>246</v>
       </c>
@@ -32418,7 +32417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>10</v>
       </c>
@@ -32447,7 +32446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>248</v>
       </c>
@@ -32476,7 +32475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>247</v>
       </c>
@@ -32505,7 +32504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>246</v>
       </c>
@@ -32534,7 +32533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>10</v>
       </c>
@@ -32563,7 +32562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>248</v>
       </c>
@@ -32592,7 +32591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>247</v>
       </c>
@@ -32621,7 +32620,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>246</v>
       </c>
@@ -32650,7 +32649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>10</v>
       </c>
@@ -32679,7 +32678,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>248</v>
       </c>
@@ -32708,7 +32707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>247</v>
       </c>
@@ -32737,7 +32736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>246</v>
       </c>
@@ -32766,7 +32765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>10</v>
       </c>
@@ -32795,7 +32794,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>248</v>
       </c>
@@ -32824,7 +32823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>247</v>
       </c>
@@ -32853,7 +32852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1057" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>246</v>
       </c>
@@ -32882,7 +32881,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1058" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1058" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>10</v>
       </c>
@@ -32911,7 +32910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1059" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1059" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>248</v>
       </c>
@@ -32940,7 +32939,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1060" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1060" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>247</v>
       </c>
@@ -32969,7 +32968,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1061" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1061" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>246</v>
       </c>
@@ -32998,7 +32997,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1062" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1062" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>10</v>
       </c>
@@ -33027,7 +33026,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1063" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1063" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>248</v>
       </c>
@@ -33056,7 +33055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1064" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1064" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
         <v>247</v>
       </c>
@@ -33085,7 +33084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1065" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1065" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
         <v>246</v>
       </c>
@@ -33114,7 +33113,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1066" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1066" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
         <v>10</v>
       </c>
@@ -33143,7 +33142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1067" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1067" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
         <v>248</v>
       </c>
@@ -33172,7 +33171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1068" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1068" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
         <v>247</v>
       </c>
@@ -33201,7 +33200,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1069" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1069" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
         <v>246</v>
       </c>
@@ -33230,7 +33229,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1070" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1070" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
         <v>10</v>
       </c>
@@ -33262,7 +33261,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="1071" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1071" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
         <v>248</v>
       </c>
@@ -33291,7 +33290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1072" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1072" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
         <v>247</v>
       </c>
@@ -33320,7 +33319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1073" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
         <v>246</v>
       </c>
@@ -33349,7 +33348,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1074" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1074" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
         <v>10</v>
       </c>
@@ -33378,7 +33377,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="1075" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1075" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
         <v>248</v>
       </c>
@@ -33407,7 +33406,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="1076" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1076" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
         <v>247</v>
       </c>
@@ -33436,7 +33435,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="1077" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1077" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
         <v>246</v>
       </c>
@@ -33465,7 +33464,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="1078" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1078" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
         <v>10</v>
       </c>
@@ -33494,7 +33493,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="1079" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1079" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
         <v>248</v>
       </c>
@@ -33523,7 +33522,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="1080" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1080" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
         <v>247</v>
       </c>
@@ -33552,7 +33551,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="1081" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1081" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
         <v>246</v>
       </c>
@@ -33581,7 +33580,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="1082" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1082" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
         <v>10</v>
       </c>
@@ -33604,13 +33603,13 @@
         <v>13</v>
       </c>
       <c r="H1082">
-        <v>7.2</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I1082">
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="1083" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
         <v>248</v>
       </c>
@@ -33633,13 +33632,13 @@
         <v>13</v>
       </c>
       <c r="H1083">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="I1083">
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="1084" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
         <v>247</v>
       </c>
@@ -33662,13 +33661,13 @@
         <v>13</v>
       </c>
       <c r="H1084">
-        <v>7.2</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="I1084">
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="1085" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
         <v>246</v>
       </c>
@@ -33694,11 +33693,11 @@
         <v>9</v>
       </c>
       <c r="I1085">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K1065">
+  <sortState ref="A2:K1065">
     <sortCondition ref="D2:D1065"/>
     <sortCondition ref="C2:C1065"/>
     <sortCondition ref="A2:A1065"/>
